--- a/EPIC_0009_Subscription_Management.xlsx
+++ b/EPIC_0009_Subscription_Management.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EIT_PROJECTS\ABCD_Framework_For_WE1_Automation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE84FE38-99A3-46AA-9DA6-DDE3756AB727}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EDD9B02-0109-465D-BAD3-0A38875EBAC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UserDriverWebIntialilzer" sheetId="43" r:id="rId1"/>
     <sheet name="SubscriptionMangement" sheetId="48" r:id="rId2"/>
+    <sheet name="DataCleanUpSheet" sheetId="49" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="41">
   <si>
     <t>Requirement Title</t>
   </si>
@@ -314,69 +315,6 @@
   </si>
   <si>
     <t>Driver Onboarding</t>
-  </si>
-  <si>
-    <t>TC_RG_01_Ride_Booking</t>
-  </si>
-  <si>
-    <t>1. Switch to the Driver App session.
-2. Grant notification permissions when prompted.
-3. Set mock/forced driver location to Perambur (13.121030, 80.232578).
-4. Accept the terms and agreements screen.
-5. Tap "Get Started" on the onboarding screen.
-6. Tap "Next" to navigate through onboarding.
-7. Tap the Mobile Number input field.
-8. Dismiss any system auto-fill popups or dialogs.
-9. Enter the approved driver mobile number.
-10. Tap "Continue".
-11. Enter the verification OTP (123456).
-12. Grant location permissions for the Driver App.
-13. Confirm reaching the Driver App landing page and ensure the online toggle status is ON.
-14. Switch to the User App session.
-15. Tap "Get Started" on the onboarding screen.
-16. Grant notification permissions when prompted.
-17. Set mock/forced user location to Perambur (13.121030, 80.232578).
-18. Tap "Next" on the onboarding screen.
-19. Tap the Mobile Number input field.
-20. Dismiss any system auto-fill popups or dialogs.
-21. Enter the customer mobile number.
-22. Tap "Continue".
-23. Enter the verification OTP (123456).
-24. Tap "Finish" to complete login.
-25. Grant location permissions for the User App.
-26. Select "Auto Ride" from the ride options.
-27. Enter the destination ("Parsn Manere") into the search field.
-28. Select the first matching destination suggestion from the list.
-29. Select the entrance location on the map.
-30. Tap "Confirm" to proceed with the selected pickup/drop location.
-31. Tap "Ride Now" to broadcast the ride request.
-32. Switch to the Driver App session.
-33. Accept the incoming ride request pop-up.
-34. Switch to the User App session.
-35. Note down/extract the displayed Ride OTP.
-36. Switch back to the Driver App session.
-37. Tap "Arrived" once reaching the pickup location.
-38. Tap "Yes" on the arrival confirmation dialog.
-39. Tap "Start Ride".
-40. Enter the extracted Ride OTP into the verification input field.
-41. Tap "Start" to officially begin the trip.
-42. Tap "Complete Ride" upon reaching the destination.
-43. Tap "Collect Payment" to initiate the cash settlement flow.
-44. Switch to the User App session.
-45. Tap "Proceed to Pay" on the payment screen.
-46. Select "Pay Cash" as the payment method.
-47. Tap "Give Review".
-48. Select the star rating by tapping the rating bar.
-49. Tap "Submit Rating".
-50. Tap "Done" to finish the trip flow on the customer side.
-51. Switch back to the Driver App session.
-52. Tap "Proceed" on the payment verification screen.
-53. Tap "Yes" to confirm receipt of the cash payment.
-54. Tap "Give Review".
-55. Select the star rating for the customer.
-56. Tap "Submit Rating".
-57. Tap "Complete" to navigate to the summary view.
-58. Tap "Submit" to finalize and clear the completed ride from the driver portal.</t>
   </si>
   <si>
     <t>This test case validates the complete end-to-end booking and fulfillment flow for an Auto Ride service between the User and Driver mobile applications. It covers logging in both an approved driver and a customer with mock location set to Perambur, initiating an auto ride request to "Parsn Manere" from the User App, accepting the booking from the Driver App, extracting the ride verification OTP, updating status to "Arrived", and entering the OTP to start the trip. Finally, it verifies completing the trip, processing a cash payment settlement on both apps, and submitting mutual ratings and reviews to successfully close out the ride lifecycle.</t>
@@ -546,14 +484,694 @@
 162.Filter Services List,type,{driverSubscriptionName},"admin.subscription.common.filter.input"
 163.Click Delete Driver  Subscription Plan,click,,"admin.subscription.driver.delete.icon"
 164.Confirm Delete Driver Subscription Plan,click,,"admin.subscription.common.dialog.btn_delete_confirm"
-165.Wait For Deletion,wait,2000,</t>
+165.Wait For Deletion,wait,2000,
+239.Click Earning Report,click,,"admin.transport.earning_reports.top_menu_btn"
+240.Click Today Button,Click,,"web.global.dashboard.today_statistics"
+241.Wait For Today Statistics,wait,2000,
+242.Click Search Button,click,,"admin.transport.earning_reports.search_btn"
+243.Wait For Load,wait,2000,
+244.Scroll Grid,tab,4,"admin.transport.earning_reports.payment_status_filter"
+245.Filter Customer Name List,type,{customerName},"admin.transport.reviews.customer_filter_name"
+246.Wait For Loading,wait,1000,
+247.Filter Driver Name List,{autoName},"admin.transport.reviews.driver_filter_name"
+248.Wait For Loading,wait,1000,
+249.Scroll Grid,tab,28,"admin.transport.earning_reports.payment_status_filter"
+250.Select Ride To Settle,click,,"admin.transport.earning_reports.ride_to_settle_select"
+251.Click Settle Transaction Button,click,"admin.transport.earning_reports.mark_as_settle_btn"
+252.Wait For Settlement,wait,2000,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.Reload User App Completely,reload_app,user,
+2.Reload Driver App Completely,reload_app,driver,
+3.Load Super Admin,switch_to,web,
+4.Click Dashboard Icon,click,,"web.global.menu.dashboard"
+5.Click Subscription Plan,click,,"admin.subscription.menu_link"
+6.Click Driver subscription plan,click,,"admin.subscription.driver.tab"
+7.Verify Driver Subscription Plan Lists ,verify,,"admin.subscription.driver.header"
+8.Click  Add New Subscription,click,,"admin.subscription.common.add_new.btn_add"
+9.Open Service Category Dropdown,click,,"admin.subscription.common.category.dropdown"
+10.Select Auto Ride,click,,"admin.subscription.common.category.option_autoride"
+11.Enter Driver Plan Name, type, DriverPlan{randomAlpha}&gt;&gt; driverSubscriptionName, "admin.subscription.common.name.input"
+12.Enter Driver Plan Name Arabic, type,عضو ذهبي, "admin.subscription.common.name_arabic.input"
+13.Enter Driver Plan Name Tamil, type,தங்க உறுப்பினர், "admin.subscription.common.name_tamil.input"
+14.Enter Driver Plan Name Hindi, type,गोल्ड मेंबर, "admin.subscription.common.name_hindi.input"
+15.Enter Number Of Days, type,100, "admin.subscription.common.days.alt_input"
+16.Enter Number Of Free Rides, type,2, "admin.subscription.driver.free_rides.input"
+17.Enter Price, type,50, "admin.subscription.common.price.input"
+18.Enter Plan Description English, type,A premium tier status offering exclusive benefits and high-level rewards to loyal users, "admin.subscription.driver.desc_english.textarea"
+19.Enter Plan Description Arabic, type,فئة عضوية مميزة تمنح المستخدمين المخلصين مزايا حصرية ومكافآت رفيعة المستوى, "admin.subscription.driver.desc_arabic.textarea"
+20.Enter Plan Description Tamil, type,இது விசுவாசமான பயனர்களுக்கு பிரத்யேக நன்மைகள் மற்றும் சலுகைகளை வழங்கும் ஒரு பிரீமியம் உறுப்பினர் நிலையாகும், "admin.subscription.driver.desc_tamil.textarea"
+21.Enter Plan Description Hindi, type,यह एक प्रीमियम सदस्यता स्तर है जो वफादार उपयोगकर्ताओं को विशेष लाभ और पुरस्कार प्रदान करता है, "admin.subscription.driver.desc_hindi.textarea"
+22.Open status Dropdown,click,,"admin.subscription.common.status.dropdown"
+23.Select On,click,,"admin.subscription.common.status.option_on"
+24.Click Submit ,click,,"web.global.action.submit"
+25.Filter Services List,type,{driverSubscriptionName},"admin.subscription.common.filter.input"
+26.Click Dashboard Icon,click,,"web.global.menu.dashboard"
+27.Click Settings Menu,click,,"web.global.menu.settings"
+28.Click Site Settings Menu,click,,"admin.setting.site_setting.sidebar_menu"
+29.Click Wallet Status Dropdown,click,,"admin.setting.site_setting.wallet_dropdown"
+30.Wait For On,wait,2000,
+31.Select Wallet ON Option,click,,"admin.setting.site_setting.walletdropdown_option_on"
+32.Click Submit Button,click,,"web.global.action.submit"
+33.Verify Settings Updated Successfully,verify,,"web.global.toast.updated"
+34.Wait For Toast To Hide,wait,3000,
+35.Click Dashboard Icon,click,,"web.global.menu.dashboard"
+36.Click drivers menu,click,,"admin.drivers.menu.icon"
+37.Click Add Driver menu,click,,"admin.drivers.add_menu.link"
+38.Verify Add Driver,verify,,"admin.drivers.add_page.header"
+39.Click Service Category Dropdown,click,,"admin.drivers.service_dropdown.select"
+40.Select Auto Ride Option,click,,"admin.drivers.service_dropdown.auto_ride"
+41.Click Driver Type Dropdown,click,,"admin.drivers.driver_type.dropdown"
+42.Select pilot Option,click,,"admin.drivers.driver_type.dropdown_pilot"
+43.Enter Driver Name, type, autodriver{randomAlpha} &gt;&gt; autoName, "admin.drivers.fullname.input"
+44.Enter Email, type, autodriver_{timestamp}@gmail.com&gt;&gt;autoEmail, "admin.drivers.email.input"
+45.Enter Contact Number, type, {randomPhone}&gt;&gt;autoPhone, "admin.drivers.phone.input"
+46.Click Whatspp, click, , "admin.drivers.whatsapp.checkbox"
+47.Enter Whatspp Number, type, {autoPhone}, "admin.drivers.whatsapp_phone.input"
+48.Upload Profile Image, uploadfile, "src/main/resources/test-data/autodriver.jpg", "admin.drivers.profile_image.file"
+49.Select Source,click,,"admin.drivers.source_dropdown.select"
+50.Select Instagram,click,,"admin.drivers.instagram_option.span"
+51.Select Male Gender, click, , "admin.drivers.male_gender.div"
+52.Click Vehicle Type Dropdown,click,,"admin.drivers.vehicle_dropdown.select"
+53. Select  Auto Option,click,,"admin.drivers.vehicle_option.pinkauto"
+54. Enter Model Year, type, 2013, "admin.drivers.modelyear.input"
+55. Enter Plate No, type, KL-01-AB-1234, "admin.drivers.plateno.input"
+56. Enter Model Name, type, petrol, "admin.drivers.modelname.input"
+57. Upload Vehicle Image, uploadfile, "src/main/resources/test-data/vehicle.jpg", "admin.drivers.vehicle_image.file"
+58. Enter Bank Name, type, HDFC Bank, "admin.drivers.bankname.input"
+59. Enter Bank Location, type, PARK STREET, "admin.drivers.banklocation.input"
+60. Enter Account Number, type, 50100123456789, "admin.drivers.accountno.input"
+61. Enter Account Holder Name, type,{autoName}, "admin.drivers.accountholder.input"
+62. Enter Payment Email Address, type, {autoEmail}, "admin.drivers.paymentemail.input"
+63. Enter IFSC Code, type, HDFC0001234, "admin.drivers.ifsc.input"
+64. Click Submit, click, , "web.global.action.submit"
+65. Verify Driver Added, verify,, "web.global.toast.success"
+66. Click Dashboard Icon,click,,"web.global.menu.dashboard"
+67. Click drivers menu,click,,"admin.drivers.menu.icon"
+68. Click Pending Documents,click,,"admin.drivers.pending_docs.link"
+69. Filter by Name,type,{autoName},"admin.drivers.name_filter.input"
+70. Scroll Grid, tab, 7, "admin.drivers.name_filter.input"
+71. Click Doc Icon,click,,"admin.drivers.docs.icon"
+72. Driver Required Documents,verify,,"admin.drivers.required_docs.header"
+73. FilterDocumet List,type,Driving Licence,"admin.drivers.docs_filter.input"
+74. Add Driving License,click,,"admin.drivers.docs.edit_icon"
+75. Upload Driving Iicense, uploadfile, "src/main/resources/test-data/license.jpg", "admin.drivers.profile_image.file"
+76. Enter Expiry Date,set_date,2026-12-12,"admin.drivers.doc_expiry.input"
+77. Click Submit, click, , "web.global.action.submit"
+78. Verify Updated Succesfully, verify, , "web.global.toast.updated"
+79. Click Approve Driver,click,,"admin.drivers.docs.approval"
+80. Verify Updated Succesfully, verify, , "web.global.toast.updated"
+81. Click Dashboard,click,,"web.global.menu.dashboard"
+82. Click drivers menu,click,,"admin.drivers.menu.icon"
+83. Click Approved Drivers,click,,"admin.drivers.approved_docs.link"
+84. Approved Drivers List,verify,,"admin.drivers.approved_page.header"
+85. Filter Approved Driver,type,{autoName},"admin.drivers.name_filter.input"
+86.Wait For Load,wait,2000,
+87.Scroll Grid,tab,10,"admin.drivers.name_filter.input"
+88.Click Wallet,click,,"admin.drivers.wallet.btn"
+89.Click Manage Transaction,click,,"admin.drivers.wallet.manage_transaction.btn"
+90.Enter Wallet Amout,type,500,"admin.drivers.wallet.wallet_amount_input"
+91.Click Dropdown,click,,"admin.drivers.wallet.option_dropdown"
+92.Select Add Money Optin,click,,"admin.drivers.wallet.option_add_money"
+93.Click Submit Button,click,,"admin.drivers.wallet.submit.btn"
+94.Wait For Recharge,wait,2000,
+95. Click Dashboard Icon,click,,"web.global.menu.dashboard"
+96.Click Customer Icon,click,,"admin.menu.customer_icon"
+97.Click Add Customers,click,,"admin.menu.add_customers"
+98.Wait For Customer Heading,wait_until_visible,,"admin.customer.add_heading"
+99.Enter Customer Name,type,customer{randomAlpha} &gt;&gt; customerName,"admin.customer.input_name"
+100.Enter Email,type,customer_{timestamp}@gmail.com&gt;&gt;customerEmail,"admin.customer.input_email"
+101.Enter Contact Number,type,{randomPhone}&gt;&gt;customerPhone,"admin.customer.input_phone"
+102.Enter Emergency Number,type,{randomPhone},"admin.customer.input_Emergency_phone"
+103.Open Gender,click,,"admin.customer.dropdown_gender"
+104.Select Male,click,,"admin.customer.select_gender_male"
+105.Upload Profile Image,uploadfile,"src/main/resources/test-data/customer.jpg","admin.customer.upload_profile_img"
+106.Click Submit,click,,"web.global.action.submit"
+107.Wait For Added Successfully,wait_until_visible,,"web.global.toast.info"
+108.Click Dashboard,click,,"web.global.menu.dashboard"
+109.Click Customer Icon,click,,"admin.menu.customer_icon"
+110.Click Verified Customers,click,,"admin.menu.verified_customers"
+111.Wait For Customer List Heading,wait_until_visible,,"admin.customer.verified_list_heading"
+112.Filter Customer Name List,type,{customerName},"admin.customer.filter_name"
+113.Wait For Load,wait,2000,
+114.Load Driver App,switch_to,driver,
+115.Wait For Notification,wait_until_visible,,"mobile.driver.permission_allow.btn"
+116.Click Allow Notification,tap,,"mobile.driver.permission_allow.btn"
+117.Click Agree,tap,,"mobile.driver.agree.btn"
+118. Click Get Started,tap,,"mobile.driver.get_started.btn"
+119.Click Next,tap,,"mobile.driver.next.btn"
+120.Click Mobile Number,tap,,"mobile.driver.mobile_number_field.btn"
+121.Click Close,tap,,"mobile.driver.cancel.btn"
+122. Enter Mobile Number,type,{autoPhone},"mobile.driver.edit_text.input"
+123.Wait for Continue,wait_until_visible,,"mobile.driver.continue.btn"
+124.Click Continue,tap,,"mobile.driver.continue.btn"
+125.Enter OTP,type,123456,"mobile.driver.edit_text.input"
+126.Enter Account Holder,type,{autoName},"mobile.driver.bank_details.account_holder_name"
+127.Enter Account Number,type,50100123456789,"mobile.driver.bank_details.account_number"
+128.Enter Confirm Account Number,type,50100123456789,"mobile.driver.bank_details.confirm_account_number"
+129.Enter IFSC Code,type,HDFC0001234,"mobile.driver.bank_details.confirm_ifsc_code"
+130.Wait For Keyboard Minimises,hide_keyboard,,
+131.Enter Upi Id,type,sujanpariyar07@fam,"mobile.driver.bank_details.upi_id"
+132.Wait For Keyboard Minimises,hide_keyboard,,
+133.Click Submit,click,,"mobile.driver.bank_details.submit_btn"
+134.Force Driver Location To Perambur,set_location,13.121030;80.232578,
+135.Click Allow Location,tap,,"mobile.driver.location_allow.btn"
+136.Wait for Toast to Hide,wait,3000,,
+137.Click Select All Agree,tap,,"mobile.driver.independent_contractor.checkbox_Select_All"
+138.Wait for Agree,wait_until_visible,,"mobile.driver.agree_continue.btn"
+139.Click Agree,tap,,"mobile.driver.agree_continue.btn"
+140.Wait For OTP,wait_until_visible,,"mobile.driver.edit_text.input"
+141. Enter OTP,type,123456,"mobile.driver.edit_text.input"
+142. Wait For Driver App,wait_until_visible,,"mobile.driver.app_header.label"
+143.Wait For Hamburger Menu,wait,3000
+144.Click Online Toggle,tap_coordinate ,975:1935,COORDINATE_MODE
+145.wait for page load,wait,3000,
+146.Click Hamburge,tap_coordinate ,75:209,COORDINATE_MODE
+147.wait for page load,wait,5000,
+148.Click Subscription,tap,,"mobile.driver.subscription.btn"
+149.Wait Driver Plan,wait_until_visible,,"mobile.driver.dynamic_subscription.plan"
+150.Click Driver Plan,tap_if_present,,"mobile.driver.dynamic_subscription.plan"
+151.Click Pay Button,tap,,"mobile.diver.subscription.pay_btn"
+152.Select Wallet Payment,tap,,"mobile.diver.subscription.select_wallet"
+153.Click Proceed to Pay,tap,,"mobile.diver.subscription.proceed_to_pay"
+154.Wait For Payment,wait,5000,
+155.Click On Payment Popup,tap_coordinate ,830:213,COORDINATE_MODE
+156.Wait To Load,wait,3000,
+157.Click back,tap,,"mobile.driver.back.btn_auto"
+158.Wait For Load,wait,3000,
+159.Load User App,switch_to,user,
+160.Wait For Get Started,wait_until_visible,,"mobile.customer.get_started.btn"
+161.Click Get Started,tap,,"mobile.customer.get_started.btn"
+162.Click Allow Notification,tap,,"mobile.customer.permission_allow.btn"
+163.Force User Location To Perambur,set_location,13.121030;80.232578,
+164.Click Next,tap,,"mobile.customer.next.btn"
+165.Click Mobile Number,tap,,"mobile.customer.mobile_number_field.btn"
+166.Click Close,tap,,"mobile.customer.cancel.btn"
+167.Enter Mobile Number,type,{customerPhone},"mobile.customer.edit_text.input"
+168.Wait for Continue,wait_until_visible,,"mobile.customer.continue.btn"
+169.Click Continue,tap,,"mobile.customer.continue.btn"
+170.Enter OTP,type,123456,"mobile.customer.otp_input"
+171.Wait for Finish,wait_until_visible,,"mobile.customer.finish.btn"
+172.Click Finish,tap,,"mobile.customer.finish.btn"
+173.Click Allow Location,tap,,"mobile.customer.location_allow.btn"
+174.Wait For Auto Ride,wait_until_visible,,"mobile.customer.auto_ride.btn"
+175.Click Auto Ride,tap,,"mobile.customer.auto_ride.btn"
+176.Enter Destination,type,Parsn Manare,"mobile.customer.destination.input"
+177.Wait for Location,wait_until_visible,,"mobile.customer.set_location_map.btn"
+178.Select Destination,tap,,"mobile.customer.destination_suggestion_first"
+179.Wait For Entrance,wait_until_visible,,"mobile.customer.destination_entrance_location"
+180.Click Entrance,tap,,"mobile.customer.destination_entrance_location"
+181.Click Confirm,tap,,"mobile.customer.confirm.btn"
+182.Wait For Ride,wait,5000,
+183.Wait for Ride,wait_until_visible,,"mobile.customer.ride_now.btn"
+184.Ride Now,tap,,"mobile.customer.ride_now.btn"
+185.Load Driver App,switch_to,driver,
+186.Wait for Accept,wait_until_visible,,"mobie.driver.auto_ride_accept.button"
+187.Click  Accept Ride,tap,,"mobie.driver.auto_ride_accept.button"
+188.Load User App,switch_to,user,
+189.Wait for OTP Layout to Load,wait_until_visible,,"mobile.customer.otp_display_element"
+190.Extract OTP from Screen,store_text,ride_otp,"mobile.customer.otp_display_element"
+191.Load Driver App,switch_to,driver,
+192.Wait for On My Way,wait_until_visible,,"mobile.driver.on_my_way.btn"
+193.Wait for Arrived,wait_until_visible,,"mobile.driver.arrived.btn"
+194.Wait for Arrived,wait_until_visible,,"mobile.driver.arrived.btn"
+195.Ride Arrived,tap,,"mobile.driver.arrived.btn"
+196.Wait for Yes,wait_until_visible,,"mobile.driver.yes.btn"
+197.Yes Arrived,tap,,"mobile.driver.yes.btn"
+198.Wait for Start Ride,wait_until_visible,,"mobile.driver.start_ride.btn"
+199.Start Ride,tap,,"mobile.driver.start_ride.btn"
+200.wait for Otp,wait_until_visible,,"mobile.driver.otp_view.input"
+201.Enter  Extracted OTP,type,{ride_otp},"mobile.driver.otp_view.input"
+202.Wait for Start Button,wait_until_visible,,"mobile.driver.start.btn"
+203.Start Ride Button,tap,,"mobile.driver.start.btn"
+204.Wait for Complete Ride,wait_until_visible,,"mobile.driver.complete_ride.btn"
+205.Complete Ride,tap,,"mobile.driver.complete_ride.btn"
+206.Wait for Collect Payment,wait_until_visible,,"mobile.driver.collect_payment.btn"
+207.Collect Payment,tap,,"mobile.driver.collect_payment.btn"
+208.Load User App,switch_to,user,
+209.Wait for Proceed Payment,wait_until_visible,,"mobile.customer.proceed_to_pay.btn"
+210.Proceed Payment,tap,,"mobile.customer.proceed_to_pay.btn"
+211.Wait for Proceed Pay Confirm,wait_until_visible,,"mobile.customer.proceed_to_pay.btn"
+212.Pay Cash,tap,,"mobile.customer.proceed_to_pay.btn"
+213.Wait for Review,wait_until_visible,,"mobile.customer.give_review.btn"
+214.Give Review,tap,,"mobile.customer.give_review.btn"
+215.Give Rating,tap_coordinate,348:1619,
+216.Submit Rating,tap,,"mobile.customer.submit_rating.btn"
+217.Wait for Done,wait_until_visible,,"mobile.customer.done.btn"
+218.Trip Finished,tap,,"mobile.customer.done.btn"
+219. Load Driver App,switch_to,driver,
+220.Wait  For Proceed,wait_until_visible,,"mobile.driver.payment.proceed_btn"
+221.Click For Proceed,tap,,"mobile.driver.payment.proceed_btn"
+222.Wait for Yes,wait_until_visible,,"mobile.driver.yes.btn"
+223.Confirm Payment,tap,,"mobile.driver.yes.btn"
+224.Wait For Give Review Button,wait_until_visible,,"mobile.driver.give_review.btn"
+225.Click Give Review Button,tap,,"mobile.driver.give_review.btn"
+226.Wait For Rating,wait,2000,
+227.Give Rating,tap_coordinate,348:1545,
+228.Submit Rating,tap,,"mobile.driver.submit_rating.btn"
+229.Wait for Complete Button,wait_until_visible,,"mobile.driver.complete.btn"
+230.Click Complete Button,tap,,"mobile.driver.complete.btn"
+231.Wait For  ride complete submit button,wait_until_visible,,"mobile.driver.ride_complete_submit.btn"
+232.Click Ride Complete Submit Button,tap,,"mobile.driver.ride_complete_submit.btn"
+233.Switch to Web,switch_to,web,
+234.Click Dashboard Icon,click,,"web.global.menu.dashboard"
+235.Click Subscription Plan,click,,"admin.subscription.menu_link"
+236.Click Driver subscription plan,click,,"admin.subscription.driver.tab"
+237.Filter Services List,type,{driverSubscriptionName},"admin.subscription.common.filter.input"
+238.Click Delete Driver  Subscription Plan,click,,"admin.subscription.driver.delete.icon"
+239.Confirm Delete Driver Subscription Plan,click,,"admin.subscription.common.dialog.btn_delete_confirm"
+240.Wait For Deletion,wait,2000,
+241.Click Dashboard Icon,click,, "web.global.menu.dashboard"
+242.Click Transport Service,Click,,"admin.transport.menu.card"
+243.Enter Services,type,Auto Ride,"admin.transport.grid.name_filter"
+244.Click Home Icon,Click,,"admin.transport.home.icon"
+245.Click Ride Button,click,,"admin.transport.ride_details.ride_top_menu_btn"
+246.Click Today Button,Click,,"web.global.dashboard.today_statistics"
+247.Click Search Button,Click,,"admin.transport.search_btn"
+248.Wait To Load,wait,2000,
+249.Filter Customer Name,type,{customerName},"admin.transport.rides.customer_name_filter_input"
+250.Wait To Load,wait,2000,
+251.Filter Driver Name,type,{autoName},"admin.transport.rides.driver_name_filter_input"
+252.Wait To Load,wait,1000,
+253.Click Ride Detail Button,click,,"admin.transport.ride_details.icon" 
+254.Wait For Ride Detail,wait,2000
+255.Show Driver Platform Fee,click,,"admin.transport.ride_details.driver_platform_fee"
+256.Wait For Ride Detail,wait,5000
+</t>
+  </si>
+  <si>
+    <t>Pre-production</t>
+  </si>
+  <si>
+    <t>QA</t>
+  </si>
+  <si>
+    <t>SA_TS_29</t>
+  </si>
+  <si>
+    <t>Clean The Test Data Created During Test Run</t>
+  </si>
+  <si>
+    <t>This test phase ensures the long-term stability and performance of the QA environment by executing a systematic Automated Data Cleanup strategy. Leveraging localized SQL Hooks with built-in safety firewalls, the workflow identifies and removes dynamically generated test artifacts—including unique City Areas, Provider profiles, and administrative accounts—created during the regression suite. By targeting specific records using variable-driven WHERE clauses, the script maintains database referential integrity, prevents record duplication in subsequent runs, and ensures the test environment remains in a pristine, 'ready-state' for continuous integration</t>
+  </si>
+  <si>
+    <t>No Manual Test Cases Since this is a data cleanup sheet after test execution</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CRITICAL SYSTEM WARNING: DATABASE INTEGRITY PROTOCOL</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>-----------------------------------------</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">This sheet contains SQL Hooks that execute directly against the we1 Production/Staging database. DO NOT modify the SQL syntax, remove variable placeholders (e.g., {areaName}), or edit the WHERE clauses.
+Unauthorized changes may result in irreversible data loss or database corruption. If modifications are required, please contact the Automation Lead or the Database Administrator.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PASSWORD TO EDIT SHEET</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> :eit6190
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Data Dependency:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> The SuperAdminLogin test suite must be always executed before this test.This ensures the browser is already logged in as a Super Admin. Without this step, the automation will encounter a "Redirect to Login" or "Access Denied" error. The framework is configured to automatically handle this login for you if it hasn't been done yet.
+RunSheet: SuperAdminLogin
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+  </si>
+  <si>
+    <t>TC_RG_03_test_data_cleanup</t>
+  </si>
+  <si>
+    <t>TC_SA_03_test_data_cleanup</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.Remove Provider Document,sql delete,,"DELETE FROM we1.required_documents WHERE name = '{providerDocumentName}';"
+</t>
+  </si>
+  <si>
+    <t>1. Reload the User App completely.
+2. Reload the Driver App completely.
+3. Switch to the Super Admin Web Portal session.
+4. Click on "Dashboard" from the navigation menu.
+5. Click on "Subscription Plan" from the navigation menu.
+6. Click on the "Driver Subscription Plan" tab.
+7. Verify that the Driver Subscription Plan header and list display correctly.
+8. Click the "Add New Subscription" button.
+9. Open the Service Category dropdown.
+10. Select "Auto Ride" from the category options.
+11. Enter a dynamic driver plan name (DriverPlan{randomAlpha}) into the Plan Name input field.
+12. Enter the plan name in Arabic (عضو ذهبي) into the Arabic name input field.
+13. Enter the plan name in Tamil (தங்க உறுப்பினர்) into the Tamil name input field.
+14. Enter the plan name in Hindi (गोल्ड मेंबर) into the Hindi name input field.
+15. Enter the number of days (100) into the duration input field.
+16. Enter the number of free rides (2) into the free rides input field.
+17. Enter the price (50) into the price input field.
+18. Enter the plan description in English into the English description field.
+19. Enter the plan description in Arabic into the Arabic description field.
+20. Enter the plan description in Tamil into the Tamil description field.
+21. Enter the plan description in Hindi into the Hindi description field.
+22. Open the Status dropdown.
+23. Select "ON" from the status options.
+24. Click the "Submit" button to create the subscription plan.
+25. Filter the subscription list by the created plan name.
+26. Click on "Dashboard" from the navigation menu.
+27. Click on "Settings" in the navigation menu.
+28. Click on "Site Settings" from the sidebar menu.
+29. Click the Wallet Status dropdown.
+30. Wait 2 seconds for dropdown options to display.
+31. Select "ON" from the Wallet Status options.
+32. Click the "Submit" button to save settings.
+33. Verify the toast notification confirms settings updated successfully.
+34. Wait 3 seconds for the toast notification to hide.
+35. Click on "Dashboard" from the navigation menu.
+36. Click on the "Drivers" menu icon.
+37. Click on the "Add Driver" link.
+38. Verify that the Add Driver page header displays.
+39. Open the Service Category dropdown.
+40. Select the "Auto Ride" option.
+41. Open the Driver Type dropdown.
+42. Select the "Pilot" option.
+43. Enter a dynamic driver name (autodriver{randomAlpha}) into the Full Name field.
+44. Enter a dynamic email address into the Email input field.
+45. Enter a dynamic phone number into the Contact Number input field.
+46. Click the WhatsApp checkbox.
+47. Enter the phone number into the WhatsApp Number input field.
+48. Upload the driver profile image from test data.
+49. Open the Source dropdown.
+50. Select "Instagram" from the options.
+51. Select "Male" as the gender.
+52. Open the Vehicle Type dropdown.
+53. Select "Auto" from the options.
+54. Enter the model year (2013) into the Model Year field.
+55. Enter the license plate number (KL-01-AB-1234) into the Plate No field.
+56. Enter the fuel/model type ("petrol") into the Model Name field.
+57. Upload the vehicle image from test data.
+58. Enter the bank name ("HDFC Bank") into the Bank Name field.
+59. Enter the bank location ("PARK STREET") into the Bank Location field.
+60. Enter the account number (50100123456789) into the Account Number field.
+61. Enter the account holder name into the Account Holder field.
+62. Enter the payment email address into the Payment Email field.
+63. Enter the IFSC code (HDFC0001234) into the IFSC Code field.
+64. Click the "Submit" button to save the new driver.
+65. Verify the toast notification confirms driver added successfully.
+66. Click on "Dashboard" from the navigation menu.
+67. Click on the "Drivers" menu icon.
+68. Click on the "Pending Documents" link.
+69. Filter the list by the newly created driver name.
+70. Tab/Scroll 7 times across the grid to locate the actions column.
+71. Click the Documents icon for the driver.
+72. Verify that the Required Documents page displays.
+73. Filter the document list by "Driving Licence".
+74. Click the Edit icon to add Driving License documents.
+75. Upload the license image from test data.
+76. Set the expiry date (2026-12-12) in the Expiry Date field.
+77. Click the "Submit" button.
+78. Verify the toast notification confirms document updated successfully.
+79. Click the "Approve Driver" button.
+80. Verify the toast notification confirms driver approved successfully.
+81. Click on "Dashboard" from the navigation menu.
+82. Click on the "Drivers" menu icon.
+83. Click on the "Approved Drivers" link.
+84. Verify that the Approved Drivers page header displays.
+85. Filter the list by the driver name.
+86. Wait 2 seconds for the search results to load.
+87. Tab/Scroll 10 times across the grid to reach the Wallet action button.
+88. Click the "Wallet" button for the approved driver.
+89. Click the "Manage Transaction" button.
+90. Enter the wallet recharge amount (500) into the amount input field.
+91. Open the transaction type dropdown.
+92. Select the "Add Money" option.
+93. Click the "Submit" button.
+94. Wait 2 seconds for the wallet recharge process to complete.
+95. Click on "Dashboard" from the navigation menu.
+96. Click on the "Customer" menu icon.
+97. Click on the "Add Customers" link.
+98. Wait for the Add Customer page heading to display.
+99. Enter a dynamic customer name (customer{randomAlpha}) into the Name field.
+100. Enter a dynamic email address into the Email field.
+101. Enter a dynamic phone number into the Contact Number field.
+102. Enter a dynamic emergency phone number.
+103. Open the Gender dropdown.
+104. Select "Male" from the options.
+105. Upload the customer profile image from test data.
+106. Click the "Submit" button.
+107. Wait for the toast notification confirming customer added successfully.
+108. Click on "Dashboard" from the navigation menu.
+109. Click on the "Customer" menu icon.
+110. Click on the "Verified Customers" link.
+111. Wait for the Verified Customers list header to display.
+112. Filter the customer list by the created customer name.
+113. Wait 2 seconds for search results to load.
+114. Switch to the Driver App session.
+115. Wait for the notification permission dialog to appear.
+116. Tap "Allow" to grant notification permissions.
+117. Tap "Agree" on the terms and conditions screen.
+118. Tap "Get Started" on the onboarding screen.
+119. Tap "Next" to navigate through onboarding.
+120. Tap the Mobile Number input field.
+121. Tap "Close" to dismiss any system auto-fill popups.
+122. Enter the generated driver mobile number.
+123. Wait for the "Continue" button to become visible.
+124. Tap "Continue".
+125. Enter the verification OTP (123456).
+126. Enter the Account Holder Name in the bank details form.
+127. Enter the Account Number in the bank details form.
+128. Enter the Confirm Account Number in the bank details form.
+129. Enter the IFSC Code in the bank details form.
+130. Dismiss/Hide the soft keyboard.
+131. Enter the UPI ID (sujanpariyar07@fam) in the bank details form.
+132. Dismiss/Hide the soft keyboard.
+133. Tap the "Submit" button on the bank details screen.
+134. Set the mock location of the Driver device to Perambur (Coordinates: 13.121030, 80.232578).
+135. Tap "Allow" to grant location permissions.
+136. Wait 3 seconds for location toast notifications to dismiss.
+137. Tap the "Select All" agreement checkbox on the contractor agreement screen.
+138. Wait for the "Agree &amp; Continue" button to become visible.
+139. Tap "Agree &amp; Continue".
+140. Wait for the OTP verification input field to display.
+141. Enter the verification OTP (123456).
+142. Wait for the Driver App home header label to display.
+143. Wait 3 seconds for the home menu elements to initialize.
+144. Tap the Online Status toggle at coordinates (975, 1935).
+145. Wait 3 seconds for the page state to update.
+146. Tap the Hamburger Menu icon at coordinates (75, 209).
+147. Wait 5 seconds for the side menu drawer to open.
+148. Tap "Subscription" from the navigation menu options.
+149. Wait for the dynamic subscription plans list to load.
+150. Tap on the newly created Driver Subscription Plan if present.
+151. Tap the "Pay" button to initiate purchase.
+152. Select "Wallet Payment" as the payment method.
+153. Tap "Proceed to Pay".
+154. Wait 5 seconds for payment processing.
+155. Tap the payment success popup at coordinates (830, 213).
+156. Wait 3 seconds for the confirmation to process.
+157. Tap the Back button on the Driver App.
+158. Wait 3 seconds for the home screen to reload.
+159. Switch to the User App session.
+160. Wait for the "Get Started" button to display on the User App screen.
+161. Tap "Get Started".
+162. Tap "Allow" to grant notification permissions.
+163. Set the mock location of the User device to Perambur (Coordinates: 13.121030, 80.232578).
+164. Tap "Next".
+165. Tap the Mobile Number input field.
+166. Tap "Close" to dismiss any system auto-fill popups.
+167. Enter the generated customer mobile number.
+168. Wait for the "Continue" button to become visible.
+169. Tap "Continue".
+170. Enter the verification OTP (123456).
+171. Wait for the "Finish" button to become visible.
+172. Tap "Finish".
+173. Tap "Allow" to grant location permissions.
+174. Wait for the "Auto Ride" option to display on the home screen.
+175. Tap "Auto Ride".
+176. Enter the destination address ("Parsn Manare") into the destination input field.
+177. Wait for the set location map selection screen to load.
+178. Tap the first destination suggestion from the list.
+179. Wait for the entrance location selector to display.
+180. Tap the entrance location option.
+181. Tap "Confirm" to set the destination.
+182. Wait 5 seconds for ride estimation and vehicle availability.
+183. Wait for the "Ride Now" button to become visible.
+184. Tap "Ride Now" to request a booking.
+185. Switch to the Driver App session.
+186. Wait for the ride request notification and Accept button to display.
+187. Tap "Accept Ride" to confirm booking.
+188. Switch to the User App session.
+189. Wait for the ride OTP layout element to display.
+190. Note down/Extract the displayed ride OTP from the screen.
+191. Switch to the Driver App session.
+192. Wait for the "On My Way" status button to display.
+193. Wait for the "Arrived" status button to display.
+194. Ensure the "Arrived" status button is fully visible.
+195. Tap "Arrived" to update driver arrival status.
+196. Wait for the confirmation dialog button ("Yes") to appear.
+197. Tap "Yes" to confirm arrival.
+198. Wait for the "Start Ride" button to display.
+199. Tap "Start Ride".
+200. Wait for the OTP input field to display.
+201. Enter the extracted ride OTP into the OTP field.
+202. Wait for the "Start" button to become visible.
+203. Tap the "Start" button to commence the trip.
+204. Wait for the "Complete Ride" button to display.
+205. Tap "Complete Ride".
+206. Wait for the "Collect Payment" button to display.
+207. Tap "Collect Payment".
+208. Switch to the User App session.
+209. Wait for the "Proceed to Pay" button to display.
+210. Tap "Proceed to Pay".
+211. Wait for the payment confirmation option to display.
+212. Tap "Pay Cash" to choose cash payment.
+213. Wait for the "Give Review" button to display.
+214. Tap "Give Review".
+215. Tap the rating stars at coordinates (348, 1619) to set rating.
+216. Tap "Submit Rating".
+217. Wait for the "Done" button to appear.
+218. Tap "Done" to finish the ride process on the customer app.
+219. Switch to the Driver App session.
+220. Wait for the payment "Proceed" button to display.
+221. Tap "Proceed".
+222. Wait for the "Yes" confirmation button to appear.
+223. Tap "Yes" to confirm receipt of payment.
+224. Wait for the "Give Review" button to display.
+225. Tap "Give Review".
+226. Wait 2 seconds for the rating screen to load.
+227. Tap the rating stars at coordinates (348, 1545) to set rating.
+228. Tap "Submit Rating".
+229. Wait for the "Complete" button to display.
+230. Tap "Complete".
+231. Wait for the final ride complete submit button to display.
+232. Tap "Ride Complete Submit".
+233. Switch to the Super Admin Web Portal session.
+234. Click on "Dashboard" from the navigation menu.
+235. Click on "Subscription Plan" from the navigation menu.
+236. Click on the "Driver Subscription Plan" tab.
+237. Filter the subscription list by the created plan name.
+238. Click the "Delete" icon for the created driver subscription plan.
+239. Click "Confirm Delete" on the confirmation modal.
+240. Wait 2 seconds for deletion process to complete.
+241. Click on "Dashboard" from the navigation menu.
+242. Click on the "Transport Service" card.
+243. Enter "Auto Ride" into the services filter field.
+244. Click the Home icon in the transport portal header.
+245. Click the "Ride" button in the top menu.
+246. Click the "Today" statistics filter button.
+247. Click the "Search" button to fetch today's rides.
+248. Wait 2 seconds for the ride records to load.
+249. Filter the ride records by the created customer name.
+250. Wait 2 seconds for results to update.
+251. Filter the ride records by the created driver name.
+252. Wait 1 second for results to update.
+253. Click the "Ride Details" icon for the completed ride.
+254. Wait 2 seconds for the ride details popup to load.
+255. Click "Show Driver Platform Fee" to verify platform commission details.
+256. verify Driver Platform Fee is Zero In ride detials</t>
+  </si>
+  <si>
+    <t>TC_RG_02_Subscription_Management</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -573,6 +1191,14 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFC00000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -604,7 +1230,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
@@ -617,6 +1243,16 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1001,8 +1637,8 @@
     <col min="6" max="6" width="45.77734375" customWidth="1"/>
     <col min="7" max="7" width="71.44140625" customWidth="1"/>
     <col min="8" max="8" width="40.44140625" customWidth="1"/>
-    <col min="9" max="9" width="61.88671875" customWidth="1"/>
-    <col min="10" max="10" width="32.88671875" customWidth="1"/>
+    <col min="9" max="9" width="31.33203125" customWidth="1"/>
+    <col min="10" max="10" width="60.21875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
@@ -1048,16 +1684,16 @@
         <v>20</v>
       </c>
       <c r="D2" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>28</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>29</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>10</v>
@@ -1065,7 +1701,9 @@
       <c r="I2" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="J2" s="2"/>
+      <c r="J2" s="2" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="1"/>
@@ -1084,4 +1722,92 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C010B387-A6F8-425E-B97E-E5006C41B202}">
+  <dimension ref="A1:J3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="3" width="24" customWidth="1"/>
+    <col min="4" max="4" width="26.77734375" customWidth="1"/>
+    <col min="5" max="6" width="34.109375" customWidth="1"/>
+    <col min="7" max="7" width="69.33203125" customWidth="1"/>
+    <col min="8" max="8" width="31.77734375" customWidth="1"/>
+    <col min="9" max="9" width="13.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="8"/>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/EPIC_0009_Subscription_Management.xlsx
+++ b/EPIC_0009_Subscription_Management.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EIT_PROJECTS\ABCD_Framework_For_WE1_Automation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EDD9B02-0109-465D-BAD3-0A38875EBAC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0403ED56-A2D0-4F03-B68B-B45B06CD42C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/EPIC_0009_Subscription_Management.xlsx
+++ b/EPIC_0009_Subscription_Management.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EIT_PROJECTS\ABCD_Framework_For_WE1_Automation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0403ED56-A2D0-4F03-B68B-B45B06CD42C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F0D6C76-555B-44CC-93A4-E87DC80B0FDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UserDriverWebIntialilzer" sheetId="43" r:id="rId1"/>
@@ -902,10 +902,6 @@
     <t>TC_SA_03_test_data_cleanup</t>
   </si>
   <si>
-    <t xml:space="preserve">1.Remove Provider Document,sql delete,,"DELETE FROM we1.required_documents WHERE name = '{providerDocumentName}';"
-</t>
-  </si>
-  <si>
     <t>1. Reload the User App completely.
 2. Reload the Driver App completely.
 3. Switch to the Super Admin Web Portal session.
@@ -1165,6 +1161,10 @@
   </si>
   <si>
     <t>TC_RG_02_Subscription_Management</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.Remove  Subscrption Plan,sql delete,,"DELETE FROM we1.subscription_plan WHERE name = '{driverSubscriptionName}';"
+</t>
   </si>
 </sst>
 </file>
@@ -1684,13 +1684,13 @@
         <v>20</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>26</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>28</v>
@@ -1790,7 +1790,7 @@
         <v>34</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>35</v>
